--- a/tests/testdata/excel/ファイル名/終わりが_.xlsx
+++ b/tests/testdata/excel/ファイル名/終わりが_.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC4D5A5C-B6CF-4494-9EB5-1BE49B2E5ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{839C26F5-28BC-482C-9BDE-FBE7DDC1D69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{FE2CC68B-AB51-4F3B-AE03-438E4F161CFE}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{4770AC95-5795-4C1E-8B3D-F2357671A6C6}"/>
   </bookViews>
   <sheets>
     <sheet name="_" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6F3CB03-70DA-477E-ACA7-A2FBDE981E97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D6D3771-781D-47BC-885E-13F40BF75B96}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
